--- a/condensate_model/HXD/analysis/data/CG_slab/Exp_concentrations.xlsx
+++ b/condensate_model/HXD/analysis/data/CG_slab/Exp_concentrations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewlatham/Documents/GitHub/Nup62_depletion_modeling/condensate_model/Surface_tension/analysis/HDX/experimental_concentration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355E24CE-CCA0-444D-9124-938E9236F232}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1731088-BD3F-E549-94D5-F377AC71A0C4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="500" windowWidth="28800" windowHeight="16400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>Time (min)</t>
   </si>
@@ -109,13 +109,13 @@
     <t>Total converstion facor:</t>
   </si>
   <si>
-    <t>Cellular concentration (mM):</t>
+    <t>microM / M</t>
   </si>
   <si>
-    <t>mM</t>
+    <t>Cellular concentration (uM):</t>
   </si>
   <si>
-    <t>microM / M</t>
+    <t>uM</t>
   </si>
 </sst>
 </file>
@@ -9925,7 +9925,7 @@
         <v>24</v>
       </c>
       <c r="R1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T1" t="s">
         <v>21</v>
@@ -9944,40 +9944,40 @@
         <v>120.14337398436916</v>
       </c>
       <c r="G2">
-        <f>1/(6.022*10^22)</f>
-        <v>1.6605778811026236E-23</v>
+        <f>1/(6.022*10^23)</f>
+        <v>1.660577881102624E-24</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="J2">
         <f>E2*$G$7</f>
-        <v>0.10621440368747069</v>
+        <v>1.062144036874707E-2</v>
       </c>
       <c r="L2">
         <f>AVERAGE(J2:J122)</f>
-        <v>0.10467178702607927</v>
+        <v>1.0467178702607922E-2</v>
       </c>
       <c r="M2" t="s">
         <v>22</v>
       </c>
       <c r="O2">
-        <f>1/(6.022*10^22)</f>
-        <v>1.6605778811026236E-23</v>
+        <f>1/(6.022*10^23)</f>
+        <v>1.660577881102624E-24</v>
       </c>
       <c r="P2" t="s">
         <v>16</v>
       </c>
       <c r="R2">
         <f>E2*$O$7</f>
-        <v>1.9950742939948383</v>
+        <v>0.19950742939948388</v>
       </c>
       <c r="T2">
         <f>AVERAGE(R2:R122)</f>
-        <v>1.9660986114152341</v>
+        <v>0.19660986114152335</v>
       </c>
       <c r="U2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -9998,7 +9998,14 @@
       </c>
       <c r="J3">
         <f t="shared" ref="J3:J66" si="1">E3*$G$7</f>
-        <v>0.1047360643049952</v>
+        <v>1.0473606430499521E-2</v>
+      </c>
+      <c r="L3">
+        <f>10^6*L2/G4</f>
+        <v>0.19660986114152326</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
       </c>
       <c r="O3">
         <f>10^15</f>
@@ -10009,7 +10016,7 @@
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R66" si="2">E3*$O$7</f>
-        <v>1.9673059612887069</v>
+        <v>0.19673059612887073</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
@@ -10029,18 +10036,18 @@
       </c>
       <c r="J4">
         <f t="shared" si="1"/>
-        <v>0.10284610054795926</v>
+        <v>1.0284610054795928E-2</v>
       </c>
       <c r="O4">
         <f>10^6</f>
         <v>1000000</v>
       </c>
       <c r="P4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R4">
         <f t="shared" si="2"/>
-        <v>1.9318058974806085</v>
+        <v>0.1931805897480609</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
@@ -10060,11 +10067,11 @@
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
-        <v>0.10084546007282535</v>
+        <v>1.0084546007282537E-2</v>
       </c>
       <c r="R5">
         <f t="shared" si="2"/>
-        <v>1.8942269416620567</v>
+        <v>0.18942269416620572</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
@@ -10078,14 +10085,14 @@
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>0.10132821579737944</v>
+        <v>1.0132821579737945E-2</v>
       </c>
       <c r="O6" t="s">
         <v>26</v>
       </c>
       <c r="R6">
         <f t="shared" si="2"/>
-        <v>1.9032947658261943</v>
+        <v>0.19032947658261948</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
@@ -10099,22 +10106,22 @@
       </c>
       <c r="G7">
         <f>G3*G4*G5*G2</f>
-        <v>8.8406376619062942E-4</v>
+        <v>8.8406376619062956E-5</v>
       </c>
       <c r="H7" t="s">
         <v>20</v>
       </c>
       <c r="J7">
         <f t="shared" si="1"/>
-        <v>9.7417777656394283E-2</v>
+        <v>9.7417777656394304E-3</v>
       </c>
       <c r="O7">
         <f>O2*O3*O4</f>
-        <v>1.6605778811026237E-2</v>
+        <v>1.6605778811026241E-3</v>
       </c>
       <c r="R7">
         <f t="shared" si="2"/>
-        <v>1.8298431967123461</v>
+        <v>0.18298431967123466</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
@@ -10128,11 +10135,11 @@
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>9.9954028550063412E-2</v>
+        <v>9.9954028550063422E-3</v>
       </c>
       <c r="R8">
         <f t="shared" si="2"/>
-        <v>1.8774827708700041</v>
+        <v>0.18774827708700045</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
@@ -10146,11 +10153,11 @@
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
-        <v>9.735668826531356E-2</v>
+        <v>9.7356688265313584E-3</v>
       </c>
       <c r="R9">
         <f t="shared" si="2"/>
-        <v>1.8286957264112411</v>
+        <v>0.18286957264112416</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
@@ -10164,11 +10171,11 @@
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
-        <v>9.8695150147909541E-2</v>
+        <v>9.8695150147909555E-3</v>
       </c>
       <c r="R10">
         <f t="shared" si="2"/>
-        <v>1.8538366753103797</v>
+        <v>0.18538366753103802</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -10182,11 +10189,11 @@
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
-        <v>9.9054134087514345E-2</v>
+        <v>9.9054134087514355E-3</v>
       </c>
       <c r="R11">
         <f t="shared" si="2"/>
-        <v>1.860579636763799</v>
+        <v>0.18605796367637994</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
@@ -10200,11 +10207,11 @@
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
-        <v>9.9660308231221587E-2</v>
+        <v>9.9660308231221614E-3</v>
       </c>
       <c r="R12">
         <f t="shared" si="2"/>
-        <v>1.8719656862053902</v>
+        <v>0.18719656862053907</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
@@ -10218,11 +10225,11 @@
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
-        <v>9.7233882308135858E-2</v>
+        <v>9.7233882308135865E-3</v>
       </c>
       <c r="R13">
         <f t="shared" si="2"/>
-        <v>1.8263890052904823</v>
+        <v>0.18263890052904827</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
@@ -10236,11 +10243,11 @@
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
-        <v>9.9304898443625569E-2</v>
+        <v>9.930489844362558E-3</v>
       </c>
       <c r="R14">
         <f t="shared" si="2"/>
-        <v>1.8652898597030507</v>
+        <v>0.18652898597030512</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
@@ -10254,11 +10261,11 @@
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
-        <v>0.10242736266375742</v>
+        <v>1.0242736266375743E-2</v>
       </c>
       <c r="R15">
         <f t="shared" si="2"/>
-        <v>1.9239405500353501</v>
+        <v>0.19239405500353507</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
@@ -10272,11 +10279,11 @@
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
-        <v>0.10263827879951691</v>
+        <v>1.0263827879951693E-2</v>
       </c>
       <c r="R16">
         <f t="shared" si="2"/>
-        <v>1.927902285412415</v>
+        <v>0.19279022854124153</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
@@ -10290,11 +10297,11 @@
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>0.10395342061160349</v>
+        <v>1.0395342061160351E-2</v>
       </c>
       <c r="R17">
         <f t="shared" si="2"/>
-        <v>1.9526052026360725</v>
+        <v>0.1952605202636073</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -10308,11 +10315,11 @@
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>0.10426420053069087</v>
+        <v>1.042642005306909E-2</v>
       </c>
       <c r="R18">
         <f t="shared" si="2"/>
-        <v>1.9584427256662391</v>
+        <v>0.19584427256662396</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
@@ -10326,11 +10333,11 @@
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>0.10296146580002001</v>
+        <v>1.0296146580002002E-2</v>
       </c>
       <c r="R19">
         <f t="shared" si="2"/>
-        <v>1.9339728563940519</v>
+        <v>0.19339728563940525</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
@@ -10344,11 +10351,11 @@
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>0.10226015233397215</v>
+        <v>1.0226015233397216E-2</v>
       </c>
       <c r="R20">
         <f t="shared" si="2"/>
-        <v>1.9207997610362748</v>
+        <v>0.19207997610362751</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
@@ -10362,11 +10369,11 @@
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>0.10203421669231619</v>
+        <v>1.020342166923162E-2</v>
       </c>
       <c r="R21">
         <f t="shared" si="2"/>
-        <v>1.9165559073298473</v>
+        <v>0.19165559073298477</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
@@ -10380,11 +10387,11 @@
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>0.10108408156057686</v>
+        <v>1.0108408156057687E-2</v>
       </c>
       <c r="R22">
         <f t="shared" si="2"/>
-        <v>1.8987090794859307</v>
+        <v>0.1898709079485931</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
@@ -10398,11 +10405,11 @@
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>9.7813614178440658E-2</v>
+        <v>9.7813614178440672E-3</v>
       </c>
       <c r="R23">
         <f t="shared" si="2"/>
-        <v>1.8372783772748877</v>
+        <v>0.18372783772748882</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
@@ -10416,11 +10423,11 @@
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
-        <v>9.8924321373253118E-2</v>
+        <v>9.8924321373253122E-3</v>
       </c>
       <c r="R24">
         <f t="shared" si="2"/>
-        <v>1.8581413044824417</v>
+        <v>0.18581413044824421</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
@@ -10434,11 +10441,11 @@
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
-        <v>9.880476090691695E-2</v>
+        <v>9.8804760906916964E-3</v>
       </c>
       <c r="R25">
         <f t="shared" si="2"/>
-        <v>1.8558955449179744</v>
+        <v>0.18558955449179748</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
@@ -10452,11 +10459,11 @@
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
-        <v>9.744607910843435E-2</v>
+        <v>9.7446079108434377E-3</v>
       </c>
       <c r="R26">
         <f t="shared" si="2"/>
-        <v>1.8303747959821965</v>
+        <v>0.1830374795982197</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
@@ -10470,11 +10477,11 @@
       </c>
       <c r="J27">
         <f t="shared" si="1"/>
-        <v>9.8345891538757724E-2</v>
+        <v>9.8345891538757745E-3</v>
       </c>
       <c r="R27">
         <f t="shared" si="2"/>
-        <v>1.8472763892391473</v>
+        <v>0.18472763892391478</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
@@ -10488,11 +10495,11 @@
       </c>
       <c r="J28">
         <f t="shared" si="1"/>
-        <v>9.9513670707881266E-2</v>
+        <v>9.951367070788128E-3</v>
       </c>
       <c r="R28">
         <f t="shared" si="2"/>
-        <v>1.8692113257496072</v>
+        <v>0.18692113257496076</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
@@ -10506,11 +10513,11 @@
       </c>
       <c r="J29">
         <f t="shared" si="1"/>
-        <v>9.8126815288883701E-2</v>
+        <v>9.8126815288883725E-3</v>
       </c>
       <c r="R29">
         <f t="shared" si="2"/>
-        <v>1.8431613786626673</v>
+        <v>0.18431613786626677</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
@@ -10524,11 +10531,11 @@
       </c>
       <c r="J30">
         <f t="shared" si="1"/>
-        <v>9.6942911160794509E-2</v>
+        <v>9.6942911160794523E-3</v>
       </c>
       <c r="R30">
         <f t="shared" si="2"/>
-        <v>1.82092355958631</v>
+        <v>0.18209235595863105</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
@@ -10542,11 +10549,11 @@
       </c>
       <c r="J31">
         <f t="shared" si="1"/>
-        <v>9.7097929011137896E-2</v>
+        <v>9.7097929011137913E-3</v>
       </c>
       <c r="R31">
         <f t="shared" si="2"/>
-        <v>1.8238353316020948</v>
+        <v>0.18238353316020953</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
@@ -10560,11 +10567,11 @@
       </c>
       <c r="J32">
         <f t="shared" si="1"/>
-        <v>9.8758944498685206E-2</v>
+        <v>9.8758944498685223E-3</v>
       </c>
       <c r="R32">
         <f t="shared" si="2"/>
-        <v>1.8550349541211246</v>
+        <v>0.1855034954121125</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
@@ -10578,11 +10585,11 @@
       </c>
       <c r="J33">
         <f t="shared" si="1"/>
-        <v>9.7820377020394922E-2</v>
+        <v>9.7820377020394946E-3</v>
       </c>
       <c r="R33">
         <f t="shared" si="2"/>
-        <v>1.8374054068647447</v>
+        <v>0.18374054068647452</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
@@ -10596,11 +10603,11 @@
       </c>
       <c r="J34">
         <f t="shared" si="1"/>
-        <v>9.9566810938037167E-2</v>
+        <v>9.9566810938037185E-3</v>
       </c>
       <c r="R34">
         <f t="shared" si="2"/>
-        <v>1.8702094832826754</v>
+        <v>0.1870209483282676</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
@@ -10614,11 +10621,11 @@
       </c>
       <c r="J35">
         <f t="shared" si="1"/>
-        <v>9.9423941389697151E-2</v>
+        <v>9.9423941389697162E-3</v>
       </c>
       <c r="R35">
         <f t="shared" si="2"/>
-        <v>1.8675258984449115</v>
+        <v>0.1867525898444912</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
@@ -10632,11 +10639,11 @@
       </c>
       <c r="J36">
         <f t="shared" si="1"/>
-        <v>0.10009824859370808</v>
+        <v>1.0009824859370809E-2</v>
       </c>
       <c r="R36">
         <f t="shared" si="2"/>
-        <v>1.8801917226860021</v>
+        <v>0.18801917226860027</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
@@ -10650,11 +10657,11 @@
       </c>
       <c r="J37">
         <f t="shared" si="1"/>
-        <v>0.10030870976306724</v>
+        <v>1.0030870976306725E-2</v>
       </c>
       <c r="R37">
         <f t="shared" si="2"/>
-        <v>1.8841449122186387</v>
+        <v>0.18841449122186391</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
@@ -10668,11 +10675,11 @@
       </c>
       <c r="J38">
         <f t="shared" si="1"/>
-        <v>0.10301280785521419</v>
+        <v>1.030128078552142E-2</v>
       </c>
       <c r="R38">
         <f t="shared" si="2"/>
-        <v>1.9349372379747287</v>
+        <v>0.19349372379747293</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
@@ -10686,11 +10693,11 @@
       </c>
       <c r="J39">
         <f t="shared" si="1"/>
-        <v>0.10190293488258845</v>
+        <v>1.0190293488258846E-2</v>
       </c>
       <c r="R39">
         <f t="shared" si="2"/>
-        <v>1.9140899803485349</v>
+        <v>0.19140899803485353</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
@@ -10704,11 +10711,11 @@
       </c>
       <c r="J40">
         <f t="shared" si="1"/>
-        <v>0.10236178855799545</v>
+        <v>1.0236178855799548E-2</v>
       </c>
       <c r="R40">
         <f t="shared" si="2"/>
-        <v>1.9227088412631357</v>
+        <v>0.19227088412631363</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
@@ -10722,11 +10729,11 @@
       </c>
       <c r="J41">
         <f t="shared" si="1"/>
-        <v>0.10207261695777094</v>
+        <v>1.0207261695777094E-2</v>
       </c>
       <c r="R41">
         <f t="shared" si="2"/>
-        <v>1.9172771972851792</v>
+        <v>0.19172771972851796</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
@@ -10740,11 +10747,11 @@
       </c>
       <c r="J42">
         <f t="shared" si="1"/>
-        <v>0.10273745532262868</v>
+        <v>1.027374553226287E-2</v>
       </c>
       <c r="R42">
         <f t="shared" si="2"/>
-        <v>1.9297651639388556</v>
+        <v>0.19297651639388561</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
@@ -10758,11 +10765,11 @@
       </c>
       <c r="J43">
         <f t="shared" si="1"/>
-        <v>0.10191307522932745</v>
+        <v>1.0191307522932748E-2</v>
       </c>
       <c r="R43">
         <f t="shared" si="2"/>
-        <v>1.9142804511736662</v>
+        <v>0.19142804511736666</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
@@ -10776,11 +10783,11 @@
       </c>
       <c r="J44">
         <f t="shared" si="1"/>
-        <v>0.10115871541050042</v>
+        <v>1.0115871541050044E-2</v>
       </c>
       <c r="R44">
         <f t="shared" si="2"/>
-        <v>1.9001109616250282</v>
+        <v>0.19001109616250289</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
@@ -10794,11 +10801,11 @@
       </c>
       <c r="J45">
         <f t="shared" si="1"/>
-        <v>0.10309046959055548</v>
+        <v>1.0309046959055551E-2</v>
       </c>
       <c r="R45">
         <f t="shared" si="2"/>
-        <v>1.9363959942867479</v>
+        <v>0.19363959942867484</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
@@ -10812,11 +10819,11 @@
       </c>
       <c r="J46">
         <f t="shared" si="1"/>
-        <v>0.10113775679545613</v>
+        <v>1.0113775679545614E-2</v>
       </c>
       <c r="R46">
         <f t="shared" si="2"/>
-        <v>1.8997172862602858</v>
+        <v>0.18997172862602862</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
@@ -10830,11 +10837,11 @@
       </c>
       <c r="J47">
         <f t="shared" si="1"/>
-        <v>0.10329973985021985</v>
+        <v>1.0329973985021987E-2</v>
       </c>
       <c r="R47">
         <f t="shared" si="2"/>
-        <v>1.9403268144115071</v>
+        <v>0.19403268144115074</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
@@ -10848,11 +10855,11 @@
       </c>
       <c r="J48">
         <f t="shared" si="1"/>
-        <v>0.10406215176519046</v>
+        <v>1.0406215176519048E-2</v>
       </c>
       <c r="R48">
         <f t="shared" si="2"/>
-        <v>1.9546475502080274</v>
+        <v>0.19546475502080279</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
@@ -10866,11 +10873,11 @@
       </c>
       <c r="J49">
         <f t="shared" si="1"/>
-        <v>0.10340315705013932</v>
+        <v>1.0340315705013934E-2</v>
       </c>
       <c r="R49">
         <f t="shared" si="2"/>
-        <v>1.9422693475327528</v>
+        <v>0.19422693475327532</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.2">
@@ -10884,11 +10891,11 @@
       </c>
       <c r="J50">
         <f t="shared" si="1"/>
-        <v>0.10300134255303592</v>
+        <v>1.0300134255303593E-2</v>
       </c>
       <c r="R50">
         <f t="shared" si="2"/>
-        <v>1.9347218798984733</v>
+        <v>0.19347218798984739</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
@@ -10902,11 +10909,11 @@
       </c>
       <c r="J51">
         <f t="shared" si="1"/>
-        <v>0.1042751386108913</v>
+        <v>1.0427513861089132E-2</v>
       </c>
       <c r="R51">
         <f t="shared" si="2"/>
-        <v>1.9586481806881186</v>
+        <v>0.19586481806881192</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.2">
@@ -10920,11 +10927,11 @@
       </c>
       <c r="J52">
         <f t="shared" si="1"/>
-        <v>0.10389316853461743</v>
+        <v>1.0389316853461743E-2</v>
       </c>
       <c r="R52">
         <f t="shared" si="2"/>
-        <v>1.9514734599930652</v>
+        <v>0.19514734599930655</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
@@ -10938,11 +10945,11 @@
       </c>
       <c r="J53">
         <f t="shared" si="1"/>
-        <v>0.10536648701166522</v>
+        <v>1.0536648701166523E-2</v>
       </c>
       <c r="R53">
         <f t="shared" si="2"/>
-        <v>1.9791474827091802</v>
+        <v>0.19791474827091807</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.2">
@@ -10956,11 +10963,11 @@
       </c>
       <c r="J54">
         <f t="shared" si="1"/>
-        <v>0.10710517271634763</v>
+        <v>1.0710517271634766E-2</v>
       </c>
       <c r="R54">
         <f t="shared" si="2"/>
-        <v>2.0118060208576876</v>
+        <v>0.20118060208576879</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
@@ -10974,11 +10981,11 @@
       </c>
       <c r="J55">
         <f t="shared" si="1"/>
-        <v>0.10596541280123355</v>
+        <v>1.0596541280123356E-2</v>
       </c>
       <c r="R55">
         <f t="shared" si="2"/>
-        <v>1.9903973829608848</v>
+        <v>0.19903973829608854</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.2">
@@ -10992,11 +10999,11 @@
       </c>
       <c r="J56">
         <f t="shared" si="1"/>
-        <v>0.10682678380921085</v>
+        <v>1.0682678380921086E-2</v>
       </c>
       <c r="R56">
         <f t="shared" si="2"/>
-        <v>2.0065769131935687</v>
+        <v>0.20065769131935693</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
@@ -11010,11 +11017,11 @@
       </c>
       <c r="J57">
         <f t="shared" si="1"/>
-        <v>0.10623355103974763</v>
+        <v>1.0623355103974766E-2</v>
       </c>
       <c r="R57">
         <f t="shared" si="2"/>
-        <v>1.9954339475728804</v>
+        <v>0.19954339475728808</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.2">
@@ -11028,11 +11035,11 @@
       </c>
       <c r="J58">
         <f t="shared" si="1"/>
-        <v>0.10857415939800903</v>
+        <v>1.0857415939800904E-2</v>
       </c>
       <c r="R58">
         <f t="shared" si="2"/>
-        <v>2.0393986774565693</v>
+        <v>0.20393986774565701</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
@@ -11046,11 +11053,11 @@
       </c>
       <c r="J59">
         <f t="shared" si="1"/>
-        <v>0.1080557445190161</v>
+        <v>1.0805574451901612E-2</v>
       </c>
       <c r="R59">
         <f t="shared" si="2"/>
-        <v>2.0296610508937305</v>
+        <v>0.20296610508937307</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.2">
@@ -11064,11 +11071,11 @@
       </c>
       <c r="J60">
         <f t="shared" si="1"/>
-        <v>0.10760434384869505</v>
+        <v>1.0760434384869505E-2</v>
       </c>
       <c r="R60">
         <f t="shared" si="2"/>
-        <v>2.0211821832224541</v>
+        <v>0.20211821832224547</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.2">
@@ -11082,11 +11089,11 @@
       </c>
       <c r="J61">
         <f t="shared" si="1"/>
-        <v>0.10628107370622644</v>
+        <v>1.0628107370622647E-2</v>
       </c>
       <c r="R61">
         <f t="shared" si="2"/>
-        <v>1.9963265878079368</v>
+        <v>0.19963265878079373</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
@@ -11100,11 +11107,11 @@
       </c>
       <c r="J62">
         <f t="shared" si="1"/>
-        <v>0.10896984098216005</v>
+        <v>1.0896984098216007E-2</v>
       </c>
       <c r="R62">
         <f t="shared" si="2"/>
-        <v>2.0468309477489268</v>
+        <v>0.20468309477489274</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
@@ -11118,11 +11125,11 @@
       </c>
       <c r="J63">
         <f t="shared" si="1"/>
-        <v>0.10792393518644952</v>
+        <v>1.0792393518644954E-2</v>
       </c>
       <c r="R63">
         <f t="shared" si="2"/>
-        <v>2.0271852152068308</v>
+        <v>0.20271852152068312</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
@@ -11136,11 +11143,11 @@
       </c>
       <c r="J64">
         <f t="shared" si="1"/>
-        <v>0.10840820734196929</v>
+        <v>1.084082073419693E-2</v>
       </c>
       <c r="R64">
         <f t="shared" si="2"/>
-        <v>2.0362815231955085</v>
+        <v>0.20362815231955089</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
@@ -11154,11 +11161,11 @@
       </c>
       <c r="J65">
         <f t="shared" si="1"/>
-        <v>0.10881222404122681</v>
+        <v>1.0881222404122683E-2</v>
       </c>
       <c r="R65">
         <f t="shared" si="2"/>
-        <v>2.0438703558118929</v>
+        <v>0.20438703558118934</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.2">
@@ -11172,11 +11179,11 @@
       </c>
       <c r="J66">
         <f t="shared" si="1"/>
-        <v>0.10835646634627021</v>
+        <v>1.0835646634627022E-2</v>
       </c>
       <c r="R66">
         <f t="shared" si="2"/>
-        <v>2.0353096481307227</v>
+        <v>0.20353096481307231</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.2">
@@ -11190,11 +11197,11 @@
       </c>
       <c r="J67">
         <f t="shared" ref="J67:J122" si="4">E67*$G$7</f>
-        <v>0.10918092514639859</v>
+        <v>1.0918092514639859E-2</v>
       </c>
       <c r="R67">
-        <f t="shared" ref="R67:R123" si="5">E67*$O$7</f>
-        <v>2.0507958392826668</v>
+        <f t="shared" ref="R67:R122" si="5">E67*$O$7</f>
+        <v>0.20507958392826672</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.2">
@@ -11208,11 +11215,11 @@
       </c>
       <c r="J68">
         <f t="shared" si="4"/>
-        <v>0.10753013505768605</v>
+        <v>1.0753013505768606E-2</v>
       </c>
       <c r="R68">
         <f t="shared" si="5"/>
-        <v>2.0197882851616402</v>
+        <v>0.20197882851616406</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.2">
@@ -11226,11 +11233,11 @@
       </c>
       <c r="J69">
         <f t="shared" si="4"/>
-        <v>0.10962620147497114</v>
+        <v>1.0962620147497116E-2</v>
       </c>
       <c r="R69">
         <f t="shared" si="5"/>
-        <v>2.0591596706089104</v>
+        <v>0.20591596706089108</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.2">
@@ -11244,11 +11251,11 @@
       </c>
       <c r="J70">
         <f t="shared" si="4"/>
-        <v>0.10996592678947574</v>
+        <v>1.0996592678947576E-2</v>
       </c>
       <c r="R70">
         <f t="shared" si="5"/>
-        <v>2.0655408883953581</v>
+        <v>0.20655408883953585</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.2">
@@ -11262,11 +11269,11 @@
       </c>
       <c r="J71">
         <f t="shared" si="4"/>
-        <v>0.10866950934641381</v>
+        <v>1.0866950934641384E-2</v>
       </c>
       <c r="R71">
         <f t="shared" si="5"/>
-        <v>2.0411896796595839</v>
+        <v>0.20411896796595844</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.2">
@@ -11280,11 +11287,11 @@
       </c>
       <c r="J72">
         <f t="shared" si="4"/>
-        <v>0.10953842546911695</v>
+        <v>1.0953842546911697E-2</v>
       </c>
       <c r="R72">
         <f t="shared" si="5"/>
-        <v>2.0575109332735808</v>
+        <v>0.20575109332735814</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.2">
@@ -11298,11 +11305,11 @@
       </c>
       <c r="J73">
         <f t="shared" si="4"/>
-        <v>0.10840759254595647</v>
+        <v>1.0840759254595649E-2</v>
       </c>
       <c r="R73">
         <f t="shared" si="5"/>
-        <v>2.0362699751975097</v>
+        <v>0.203626997519751</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.2">
@@ -11316,11 +11323,11 @@
       </c>
       <c r="J74">
         <f t="shared" si="4"/>
-        <v>0.10998074466565318</v>
+        <v>1.0998074466565319E-2</v>
       </c>
       <c r="R74">
         <f t="shared" si="5"/>
-        <v>2.0658192194204061</v>
+        <v>0.20658192194204064</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.2">
@@ -11334,11 +11341,11 @@
       </c>
       <c r="J75">
         <f t="shared" si="4"/>
-        <v>0.10992554291205434</v>
+        <v>1.0992554291205435E-2</v>
       </c>
       <c r="R75">
         <f t="shared" si="5"/>
-        <v>2.0647823393385618</v>
+        <v>0.20647823393385623</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.2">
@@ -11352,11 +11359,11 @@
       </c>
       <c r="J76">
         <f t="shared" si="4"/>
-        <v>0.10752666178857792</v>
+        <v>1.0752666178857794E-2</v>
       </c>
       <c r="R76">
         <f t="shared" si="5"/>
-        <v>2.0197230451407653</v>
+        <v>0.20197230451407661</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.2">
@@ -11370,11 +11377,11 @@
       </c>
       <c r="J77">
         <f t="shared" si="4"/>
-        <v>0.10598163918666638</v>
+        <v>1.059816391866664E-2</v>
       </c>
       <c r="R77">
         <f t="shared" si="5"/>
-        <v>1.9907021706670489</v>
+        <v>0.19907021706670494</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.2">
@@ -11388,11 +11395,11 @@
       </c>
       <c r="J78">
         <f t="shared" si="4"/>
-        <v>0.10685256280022443</v>
+        <v>1.0685256280022443E-2</v>
       </c>
       <c r="R78">
         <f t="shared" si="5"/>
-        <v>2.0070611319107181</v>
+        <v>0.20070611319107184</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.2">
@@ -11406,11 +11413,11 @@
       </c>
       <c r="J79">
         <f t="shared" si="4"/>
-        <v>0.10711328195017683</v>
+        <v>1.0711328195017685E-2</v>
       </c>
       <c r="R79">
         <f t="shared" si="5"/>
-        <v>2.011958340349159</v>
+        <v>0.20119583403491592</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
@@ -11424,11 +11431,11 @@
       </c>
       <c r="J80">
         <f t="shared" si="4"/>
-        <v>0.1059907373797328</v>
+        <v>1.0599073737973282E-2</v>
       </c>
       <c r="R80">
         <f t="shared" si="5"/>
-        <v>1.9908730662375034</v>
+        <v>0.19908730662375038</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.2">
@@ -11442,11 +11449,11 @@
       </c>
       <c r="J81">
         <f t="shared" si="4"/>
-        <v>0.10824286845536876</v>
+        <v>1.0824286845536877E-2</v>
       </c>
       <c r="R81">
         <f t="shared" si="5"/>
-        <v>2.0331758863797611</v>
+        <v>0.20331758863797617</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.2">
@@ -11460,11 +11467,11 @@
       </c>
       <c r="J82">
         <f t="shared" si="4"/>
-        <v>0.10740405147161527</v>
+        <v>1.0740405147161529E-2</v>
       </c>
       <c r="R82">
         <f t="shared" si="5"/>
-        <v>2.0174199988206967</v>
+        <v>0.2017419998820697</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.2">
@@ -11478,11 +11485,11 @@
       </c>
       <c r="J83">
         <f t="shared" si="4"/>
-        <v>0.10956468682360328</v>
+        <v>1.095646868236033E-2</v>
       </c>
       <c r="R83">
         <f t="shared" si="5"/>
-        <v>2.0580042124470475</v>
+        <v>0.2058004212447048</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.2">
@@ -11496,11 +11503,11 @@
       </c>
       <c r="J84">
         <f t="shared" si="4"/>
-        <v>0.10921993281195083</v>
+        <v>1.0921993281195086E-2</v>
       </c>
       <c r="R84">
         <f t="shared" si="5"/>
-        <v>2.0515285383150981</v>
+        <v>0.20515285383150986</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.2">
@@ -11514,11 +11521,11 @@
       </c>
       <c r="J85">
         <f t="shared" si="4"/>
-        <v>0.10998305305300748</v>
+        <v>1.099830530530075E-2</v>
       </c>
       <c r="R85">
         <f t="shared" si="5"/>
-        <v>2.0658625789282623</v>
+        <v>0.20658625789282631</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.2">
@@ -11532,11 +11539,11 @@
       </c>
       <c r="J86">
         <f t="shared" si="4"/>
-        <v>0.11266545353161254</v>
+        <v>1.1266545353161257E-2</v>
       </c>
       <c r="R86">
         <f t="shared" si="5"/>
-        <v>2.1162473483688662</v>
+        <v>0.21162473483688668</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.2">
@@ -11550,11 +11557,11 @@
       </c>
       <c r="J87">
         <f t="shared" si="4"/>
-        <v>0.11199200052866652</v>
+        <v>1.1199200052866653E-2</v>
       </c>
       <c r="R87">
         <f t="shared" si="5"/>
-        <v>2.1035975689816495</v>
+        <v>0.21035975689816502</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.2">
@@ -11568,11 +11575,11 @@
       </c>
       <c r="J88">
         <f t="shared" si="4"/>
-        <v>0.1119131183922656</v>
+        <v>1.1191311839226562E-2</v>
       </c>
       <c r="R88">
         <f t="shared" si="5"/>
-        <v>2.1021158893118006</v>
+        <v>0.21021158893118011</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.2">
@@ -11586,11 +11593,11 @@
       </c>
       <c r="J89">
         <f t="shared" si="4"/>
-        <v>0.11196089806693585</v>
+        <v>1.1196089806693586E-2</v>
       </c>
       <c r="R89">
         <f t="shared" si="5"/>
-        <v>2.1030133570506448</v>
+        <v>0.21030133570506451</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.2">
@@ -11604,11 +11611,11 @@
       </c>
       <c r="J90">
         <f t="shared" si="4"/>
-        <v>0.11204180257742659</v>
+        <v>1.120418025774266E-2</v>
       </c>
       <c r="R90">
         <f t="shared" si="5"/>
-        <v>2.1045330239088536</v>
+        <v>0.21045330239088542</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.2">
@@ -11622,11 +11629,11 @@
       </c>
       <c r="J91">
         <f t="shared" si="4"/>
-        <v>0.10989424248434727</v>
+        <v>1.0989424248434729E-2</v>
       </c>
       <c r="R91">
         <f t="shared" si="5"/>
-        <v>2.0641944089210158</v>
+        <v>0.20641944089210162</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.2">
@@ -11640,11 +11647,11 @@
       </c>
       <c r="J92">
         <f t="shared" si="4"/>
-        <v>0.10856556415419383</v>
+        <v>1.0856556415419385E-2</v>
       </c>
       <c r="R92">
         <f t="shared" si="5"/>
-        <v>2.0392372290146352</v>
+        <v>0.20392372290146357</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.2">
@@ -11658,11 +11665,11 @@
       </c>
       <c r="J93">
         <f t="shared" si="4"/>
-        <v>0.10785054183488409</v>
+        <v>1.0785054183488411E-2</v>
       </c>
       <c r="R93">
         <f t="shared" si="5"/>
-        <v>2.0258066339224206</v>
+        <v>0.20258066339224212</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.2">
@@ -11676,11 +11683,11 @@
       </c>
       <c r="J94">
         <f t="shared" si="4"/>
-        <v>0.10994373730254499</v>
+        <v>1.0994373730254501E-2</v>
       </c>
       <c r="R94">
         <f t="shared" si="5"/>
-        <v>2.0651240929943997</v>
+        <v>0.20651240929944001</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.2">
@@ -11694,11 +11701,11 @@
       </c>
       <c r="J95">
         <f t="shared" si="4"/>
-        <v>0.10816684805497401</v>
+        <v>1.0816684805497403E-2</v>
       </c>
       <c r="R95">
         <f t="shared" si="5"/>
-        <v>2.0317479600215527</v>
+        <v>0.20317479600215529</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.2">
@@ -11712,11 +11719,11 @@
       </c>
       <c r="J96">
         <f t="shared" si="4"/>
-        <v>0.10609633332682505</v>
+        <v>1.0609633332682507E-2</v>
       </c>
       <c r="R96">
         <f t="shared" si="5"/>
-        <v>1.9928565237750862</v>
+        <v>0.19928565237750867</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.2">
@@ -11730,11 +11737,11 @@
       </c>
       <c r="J97">
         <f t="shared" si="4"/>
-        <v>0.10527377966107779</v>
+        <v>1.052737796610778E-2</v>
       </c>
       <c r="R97">
         <f t="shared" si="5"/>
-        <v>1.977406117643802</v>
+        <v>0.19774061176438024</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.2">
@@ -11748,11 +11755,11 @@
       </c>
       <c r="J98">
         <f t="shared" si="4"/>
-        <v>0.10676647023155855</v>
+        <v>1.0676647023155857E-2</v>
       </c>
       <c r="R98">
         <f t="shared" si="5"/>
-        <v>2.005444015355089</v>
+        <v>0.20054440153550895</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.2">
@@ -11766,11 +11773,11 @@
       </c>
       <c r="J99">
         <f t="shared" si="4"/>
-        <v>0.1066564998491441</v>
+        <v>1.0665649984914413E-2</v>
       </c>
       <c r="R99">
         <f t="shared" si="5"/>
-        <v>2.0033783907746283</v>
+        <v>0.20033783907746286</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.2">
@@ -11784,11 +11791,11 @@
       </c>
       <c r="J100">
         <f t="shared" si="4"/>
-        <v>0.10506569521564872</v>
+        <v>1.0506569521564875E-2</v>
       </c>
       <c r="R100">
         <f t="shared" si="5"/>
-        <v>1.973497571216547</v>
+        <v>0.19734975712165473</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.2">
@@ -11802,11 +11809,11 @@
       </c>
       <c r="J101">
         <f t="shared" si="4"/>
-        <v>0.10608692509746434</v>
+        <v>1.0608692509746435E-2</v>
       </c>
       <c r="R101">
         <f t="shared" si="5"/>
-        <v>1.9926798046494505</v>
+        <v>0.19926798046494509</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.2">
@@ -11820,11 +11827,11 @@
       </c>
       <c r="J102">
         <f t="shared" si="4"/>
-        <v>0.10730849735018123</v>
+        <v>1.0730849735018125E-2</v>
       </c>
       <c r="R102">
         <f t="shared" si="5"/>
-        <v>2.0156251615411951</v>
+        <v>0.20156251615411955</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.2">
@@ -11838,11 +11845,11 @@
       </c>
       <c r="J103">
         <f t="shared" si="4"/>
-        <v>0.10623196928293102</v>
+        <v>1.0623196928293104E-2</v>
       </c>
       <c r="R103">
         <f t="shared" si="5"/>
-        <v>1.9954042367026537</v>
+        <v>0.19954042367026539</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.2">
@@ -11856,11 +11863,11 @@
       </c>
       <c r="J104">
         <f t="shared" si="4"/>
-        <v>0.10774409593515881</v>
+        <v>1.0774409593515883E-2</v>
       </c>
       <c r="R104">
         <f t="shared" si="5"/>
-        <v>2.0238072113312255</v>
+        <v>0.20238072113312261</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.2">
@@ -11874,11 +11881,11 @@
       </c>
       <c r="J105">
         <f t="shared" si="4"/>
-        <v>0.105545254634221</v>
+        <v>1.0554525463422101E-2</v>
       </c>
       <c r="R105">
         <f t="shared" si="5"/>
-        <v>1.9825053576863731</v>
+        <v>0.19825053576863735</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.2">
@@ -11892,11 +11899,11 @@
       </c>
       <c r="J106">
         <f t="shared" si="4"/>
-        <v>0.10512150654615851</v>
+        <v>1.0512150654615852E-2</v>
       </c>
       <c r="R106">
         <f t="shared" si="5"/>
-        <v>1.9745459012635842</v>
+        <v>0.19745459012635846</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.2">
@@ -11910,11 +11917,11 @@
       </c>
       <c r="J107">
         <f t="shared" si="4"/>
-        <v>0.10831047861410288</v>
+        <v>1.0831047861410288E-2</v>
       </c>
       <c r="R107">
         <f t="shared" si="5"/>
-        <v>2.0344458392771125</v>
+        <v>0.20344458392771128</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.2">
@@ -11928,11 +11935,11 @@
       </c>
       <c r="J108">
         <f t="shared" si="4"/>
-        <v>0.1070735272947141</v>
+        <v>1.0707352729471412E-2</v>
       </c>
       <c r="R108">
         <f t="shared" si="5"/>
-        <v>2.0112116102595778</v>
+        <v>0.20112116102595784</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.2">
@@ -11946,11 +11953,11 @@
       </c>
       <c r="J109">
         <f t="shared" si="4"/>
-        <v>0.10504794295283637</v>
+        <v>1.0504794295283639E-2</v>
       </c>
       <c r="R109">
         <f t="shared" si="5"/>
-        <v>1.9731641222494802</v>
+        <v>0.19731641222494808</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.2">
@@ -11964,11 +11971,11 @@
       </c>
       <c r="J110">
         <f t="shared" si="4"/>
-        <v>0.10723847609723242</v>
+        <v>1.0723847609723242E-2</v>
       </c>
       <c r="R110">
         <f t="shared" si="5"/>
-        <v>2.0143099199455019</v>
+        <v>0.20143099199455022</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.2">
@@ -11982,11 +11989,11 @@
       </c>
       <c r="J111">
         <f t="shared" si="4"/>
-        <v>0.10396557574265766</v>
+        <v>1.0396557574265768E-2</v>
       </c>
       <c r="R111">
         <f t="shared" si="5"/>
-        <v>1.9528335180873146</v>
+        <v>0.19528335180873149</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.2">
@@ -12000,11 +12007,11 @@
       </c>
       <c r="J112">
         <f t="shared" si="4"/>
-        <v>0.10455728846619526</v>
+        <v>1.0455728846619527E-2</v>
       </c>
       <c r="R112">
         <f t="shared" si="5"/>
-        <v>1.9639479319819979</v>
+        <v>0.19639479319819986</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.2">
@@ -12018,11 +12025,11 @@
       </c>
       <c r="J113">
         <f t="shared" si="4"/>
-        <v>0.10611354023576496</v>
+        <v>1.0611354023576497E-2</v>
       </c>
       <c r="R113">
         <f t="shared" si="5"/>
-        <v>1.9931797291080098</v>
+        <v>0.19931797291080103</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.2">
@@ -12036,11 +12043,11 @@
       </c>
       <c r="J114">
         <f t="shared" si="4"/>
-        <v>0.10443373469037738</v>
+        <v>1.044337346903774E-2</v>
       </c>
       <c r="R114">
         <f t="shared" si="5"/>
-        <v>1.9616271642376764</v>
+        <v>0.19616271642376767</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.2">
@@ -12054,11 +12061,11 @@
       </c>
       <c r="J115">
         <f t="shared" si="4"/>
-        <v>0.10404518031602211</v>
+        <v>1.0404518031602214E-2</v>
       </c>
       <c r="R115">
         <f t="shared" si="5"/>
-        <v>1.9543287676249494</v>
+        <v>0.19543287676249499</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.2">
@@ -12072,11 +12079,11 @@
       </c>
       <c r="J116">
         <f t="shared" si="4"/>
-        <v>0.10316156706717554</v>
+        <v>1.0316156706717556E-2</v>
       </c>
       <c r="R116">
         <f t="shared" si="5"/>
-        <v>1.9377314510896684</v>
+        <v>0.19377314510896687</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.2">
@@ -12090,11 +12097,11 @@
       </c>
       <c r="J117">
         <f t="shared" si="4"/>
-        <v>0.10364853009163193</v>
+        <v>1.0364853009163193E-2</v>
       </c>
       <c r="R117">
         <f t="shared" si="5"/>
-        <v>1.9468783029147521</v>
+        <v>0.19468783029147524</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.2">
@@ -12108,11 +12115,11 @@
       </c>
       <c r="J118">
         <f t="shared" si="4"/>
-        <v>0.10260112098816684</v>
+        <v>1.0260112098816686E-2</v>
       </c>
       <c r="R118">
         <f t="shared" si="5"/>
-        <v>1.9272043330474631</v>
+        <v>0.19272043330474634</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.2">
@@ -12126,11 +12133,11 @@
       </c>
       <c r="J119">
         <f t="shared" si="4"/>
-        <v>0.10435956671383051</v>
+        <v>1.0435956671383053E-2</v>
       </c>
       <c r="R119">
         <f t="shared" si="5"/>
-        <v>1.9602340328137908</v>
+        <v>0.19602340328137913</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.2">
@@ -12144,11 +12151,11 @@
       </c>
       <c r="J120">
         <f t="shared" si="4"/>
-        <v>0.10711863960719137</v>
+        <v>1.0711863960719138E-2</v>
       </c>
       <c r="R120">
         <f t="shared" si="5"/>
-        <v>2.0120589757000591</v>
+        <v>0.20120589757000595</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.2">
@@ -12162,11 +12169,11 @@
       </c>
       <c r="J121">
         <f t="shared" si="4"/>
-        <v>0.10412147017872522</v>
+        <v>1.0412147017872523E-2</v>
       </c>
       <c r="R121">
         <f t="shared" si="5"/>
-        <v>1.9557617554183866</v>
+        <v>0.1955761755418387</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.2">
@@ -12180,11 +12187,11 @@
       </c>
       <c r="J122">
         <f t="shared" si="4"/>
-        <v>0.1048248396263842</v>
+        <v>1.0482483962638421E-2</v>
       </c>
       <c r="R122">
         <f t="shared" si="5"/>
-        <v>1.9689734692301482</v>
+        <v>0.19689734692301486</v>
       </c>
     </row>
   </sheetData>
